--- a/artfynd/A 61433-2025 artfynd.xlsx
+++ b/artfynd/A 61433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130792129</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130792131</v>
+        <v>130792123</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540369</v>
+        <v>540374</v>
       </c>
       <c r="R3" t="n">
-        <v>6983365</v>
+        <v>6983624</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Relativt rikligt med långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -947,10 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130792123</v>
+        <v>130792131</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540374</v>
+        <v>540369</v>
       </c>
       <c r="R4" t="n">
-        <v>6983624</v>
+        <v>6983365</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Relativt rikligt med långväxta bålar på flera granar.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1086,7 +1086,7 @@
         <v>130792114</v>
       </c>
       <c r="B5" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>130792121</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>130792118</v>
       </c>
       <c r="B7" t="n">
-        <v>80352</v>
+        <v>80360</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>130792119</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>130792115</v>
       </c>
       <c r="B9" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>130792125</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>130792116</v>
       </c>
       <c r="B11" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2003,37 +2003,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130792126</v>
+        <v>130792111</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>80353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2041,10 +2045,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540352</v>
+        <v>540437</v>
       </c>
       <c r="R12" t="n">
-        <v>6983522</v>
+        <v>6983501</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2081,7 +2085,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Garnlav på en stående död gran med full längd och 26 cm i brösthöjdsdiameter.</t>
+          <t>På en tvåstammig sälg i bra skick.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2106,22 +2110,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2139,41 +2143,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130792111</v>
+        <v>130792126</v>
       </c>
       <c r="B13" t="n">
-        <v>80345</v>
+        <v>79219</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540437</v>
+        <v>540352</v>
       </c>
       <c r="R13" t="n">
-        <v>6983501</v>
+        <v>6983522</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en tvåstammig sälg i bra skick.</t>
+          <t>Garnlav på en stående död gran med full längd och 26 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2246,22 +2246,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2282,7 +2282,7 @@
         <v>130792107</v>
       </c>
       <c r="B14" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130792127</v>
+        <v>130792132</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540394</v>
+        <v>540329</v>
       </c>
       <c r="R15" t="n">
-        <v>6983545</v>
+        <v>6983376</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På flera granar i tät äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2501,6 +2501,11 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2538,10 +2543,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130792132</v>
+        <v>130792127</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2576,10 +2581,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540329</v>
+        <v>540394</v>
       </c>
       <c r="R16" t="n">
-        <v>6983376</v>
+        <v>6983545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2616,7 +2621,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På flera granar i tät äldre flerskiktad granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2632,11 +2637,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2674,41 +2674,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130792112</v>
+        <v>130792120</v>
       </c>
       <c r="B17" t="n">
-        <v>80345</v>
+        <v>79219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2716,10 +2712,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540538</v>
+        <v>540423</v>
       </c>
       <c r="R17" t="n">
-        <v>6983440</v>
+        <v>6983752</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2756,7 +2752,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På en levande skadad sälg.</t>
+          <t>På en stående död högväxt gran med full längd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2781,22 +2777,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2814,37 +2810,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130792120</v>
+        <v>130792112</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>80353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540423</v>
+        <v>540538</v>
       </c>
       <c r="R18" t="n">
-        <v>6983752</v>
+        <v>6983440</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På en stående död högväxt gran med full längd.</t>
+          <t>På en levande skadad sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2917,22 +2917,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
         <v>130792110</v>
       </c>
       <c r="B19" t="n">
-        <v>80345</v>
+        <v>80353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>130792128</v>
       </c>
       <c r="B20" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>130792124</v>
       </c>
       <c r="B21" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>130792122</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>130792113</v>
       </c>
       <c r="B23" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>130792130</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>130792117</v>
       </c>
       <c r="B25" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>130792108</v>
       </c>
       <c r="B26" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>130792106</v>
       </c>
       <c r="B27" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 61433-2025 artfynd.xlsx
+++ b/artfynd/A 61433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130792129</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130792123</v>
+        <v>130792131</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540374</v>
+        <v>540369</v>
       </c>
       <c r="R3" t="n">
-        <v>6983624</v>
+        <v>6983365</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Relativt rikligt med långväxta bålar på flera granar.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -947,10 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130792131</v>
+        <v>130792123</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540369</v>
+        <v>540374</v>
       </c>
       <c r="R4" t="n">
-        <v>6983365</v>
+        <v>6983624</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Relativt rikligt med långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1086,7 +1086,7 @@
         <v>130792114</v>
       </c>
       <c r="B5" t="n">
-        <v>97841</v>
+        <v>97842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>130792121</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1331,41 +1331,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130792118</v>
+        <v>130792119</v>
       </c>
       <c r="B7" t="n">
-        <v>80360</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1373,10 +1369,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540442</v>
+        <v>540399</v>
       </c>
       <c r="R7" t="n">
-        <v>6983512</v>
+        <v>6983725</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,6 +1407,11 @@
           <t>2026-01-19</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1426,24 +1427,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1461,37 +1467,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130792119</v>
+        <v>130792118</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>80361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1499,10 +1509,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540399</v>
+        <v>540442</v>
       </c>
       <c r="R8" t="n">
-        <v>6983725</v>
+        <v>6983512</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1537,11 +1547,6 @@
           <t>2026-01-19</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gammal gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1557,29 +1562,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130792115</v>
+        <v>130792125</v>
       </c>
       <c r="B9" t="n">
-        <v>80324</v>
+        <v>79220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,30 +1608,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1639,10 +1635,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540440</v>
+        <v>540336</v>
       </c>
       <c r="R9" t="n">
-        <v>6983516</v>
+        <v>6983550</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1677,6 +1673,11 @@
           <t>2026-01-19</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1692,29 +1693,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1732,10 +1728,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130792125</v>
+        <v>130792115</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>80325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,26 +1739,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540336</v>
+        <v>540440</v>
       </c>
       <c r="R10" t="n">
-        <v>6983550</v>
+        <v>6983516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1808,11 +1808,6 @@
           <t>2026-01-19</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1828,24 +1823,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
+        </is>
+      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1866,7 +1866,7 @@
         <v>130792116</v>
       </c>
       <c r="B11" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2003,41 +2003,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130792111</v>
+        <v>130792126</v>
       </c>
       <c r="B12" t="n">
-        <v>80353</v>
+        <v>79220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2045,10 +2041,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540437</v>
+        <v>540352</v>
       </c>
       <c r="R12" t="n">
-        <v>6983501</v>
+        <v>6983522</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2085,7 +2081,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en tvåstammig sälg i bra skick.</t>
+          <t>Garnlav på en stående död gran med full längd och 26 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2110,22 +2106,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2143,37 +2139,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130792126</v>
+        <v>130792111</v>
       </c>
       <c r="B13" t="n">
-        <v>79219</v>
+        <v>80354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540352</v>
+        <v>540437</v>
       </c>
       <c r="R13" t="n">
-        <v>6983522</v>
+        <v>6983501</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Garnlav på en stående död gran med full längd och 26 cm i brösthöjdsdiameter.</t>
+          <t>På en tvåstammig sälg i bra skick.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2246,22 +2246,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2282,7 +2282,7 @@
         <v>130792107</v>
       </c>
       <c r="B14" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>130792132</v>
       </c>
       <c r="B15" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130792127</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>130792120</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>130792112</v>
       </c>
       <c r="B18" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>130792110</v>
       </c>
       <c r="B19" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>130792128</v>
       </c>
       <c r="B20" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>130792124</v>
       </c>
       <c r="B21" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>130792122</v>
       </c>
       <c r="B22" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>130792113</v>
       </c>
       <c r="B23" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>130792130</v>
       </c>
       <c r="B24" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>130792117</v>
       </c>
       <c r="B25" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>130792108</v>
       </c>
       <c r="B26" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>130792106</v>
       </c>
       <c r="B27" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 61433-2025 artfynd.xlsx
+++ b/artfynd/A 61433-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130792129</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>130792131</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>130792123</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>130792114</v>
       </c>
       <c r="B5" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>130792121</v>
       </c>
       <c r="B6" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>130792119</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>130792118</v>
       </c>
       <c r="B8" t="n">
-        <v>80361</v>
+        <v>80362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130792125</v>
+        <v>130792116</v>
       </c>
       <c r="B9" t="n">
-        <v>79220</v>
+        <v>80326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,26 +1608,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1635,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540336</v>
+        <v>540533</v>
       </c>
       <c r="R9" t="n">
-        <v>6983550</v>
+        <v>6983434</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1675,7 +1679,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Fertil lunglav med apothecier på en skadad men levande sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1693,24 +1697,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1731,7 +1740,7 @@
         <v>130792115</v>
       </c>
       <c r="B10" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1863,10 +1872,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130792116</v>
+        <v>130792125</v>
       </c>
       <c r="B11" t="n">
-        <v>80325</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,30 +1883,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1905,10 +1910,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540533</v>
+        <v>540336</v>
       </c>
       <c r="R11" t="n">
-        <v>6983434</v>
+        <v>6983550</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1945,7 +1950,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på en skadad men levande sälg.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1963,29 +1968,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
         <v>130792126</v>
       </c>
       <c r="B12" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>130792111</v>
       </c>
       <c r="B13" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>130792107</v>
       </c>
       <c r="B14" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>130792132</v>
       </c>
       <c r="B15" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130792127</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2674,37 +2674,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130792120</v>
+        <v>130792112</v>
       </c>
       <c r="B17" t="n">
-        <v>79220</v>
+        <v>80355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2712,10 +2716,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540423</v>
+        <v>540538</v>
       </c>
       <c r="R17" t="n">
-        <v>6983752</v>
+        <v>6983440</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2752,7 +2756,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På en stående död högväxt gran med full längd.</t>
+          <t>På en levande skadad sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2777,22 +2781,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2810,41 +2814,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130792112</v>
+        <v>130792120</v>
       </c>
       <c r="B18" t="n">
-        <v>80354</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540538</v>
+        <v>540423</v>
       </c>
       <c r="R18" t="n">
-        <v>6983440</v>
+        <v>6983752</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På en levande skadad sälg.</t>
+          <t>På en stående död högväxt gran med full längd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2917,22 +2917,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
         <v>130792110</v>
       </c>
       <c r="B19" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>130792128</v>
       </c>
       <c r="B20" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>130792124</v>
       </c>
       <c r="B21" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>130792122</v>
       </c>
       <c r="B22" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>130792113</v>
       </c>
       <c r="B23" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>130792130</v>
       </c>
       <c r="B24" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>130792117</v>
       </c>
       <c r="B25" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>130792108</v>
       </c>
       <c r="B26" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>130792106</v>
       </c>
       <c r="B27" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 61433-2025 artfynd.xlsx
+++ b/artfynd/A 61433-2025 artfynd.xlsx
@@ -1331,37 +1331,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130792119</v>
+        <v>130792118</v>
       </c>
       <c r="B7" t="n">
-        <v>79221</v>
+        <v>80362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1369,10 +1373,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540399</v>
+        <v>540442</v>
       </c>
       <c r="R7" t="n">
-        <v>6983725</v>
+        <v>6983512</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,11 +1411,6 @@
           <t>2026-01-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal gran.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1427,29 +1426,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
-        </is>
-      </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,41 +1461,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130792118</v>
+        <v>130792119</v>
       </c>
       <c r="B8" t="n">
-        <v>80362</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1509,10 +1499,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540442</v>
+        <v>540399</v>
       </c>
       <c r="R8" t="n">
-        <v>6983512</v>
+        <v>6983725</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1547,6 +1537,11 @@
           <t>2026-01-19</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1562,24 +1557,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130792116</v>
+        <v>130792125</v>
       </c>
       <c r="B9" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,30 +1608,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1639,10 +1635,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540533</v>
+        <v>540336</v>
       </c>
       <c r="R9" t="n">
-        <v>6983434</v>
+        <v>6983550</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1679,7 +1675,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på en skadad men levande sälg.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,29 +1693,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1872,10 +1863,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130792125</v>
+        <v>130792116</v>
       </c>
       <c r="B11" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,26 +1874,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1910,10 +1905,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540336</v>
+        <v>540533</v>
       </c>
       <c r="R11" t="n">
-        <v>6983550</v>
+        <v>6983434</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1950,7 +1945,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Fertil lunglav med apothecier på en skadad men levande sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1968,24 +1963,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130792130</v>
+        <v>130792117</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3644,26 +3644,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3671,10 +3675,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540421</v>
+        <v>540356</v>
       </c>
       <c r="R24" t="n">
-        <v>6983424</v>
+        <v>6983351</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3711,7 +3715,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På flera granar i flerskiktad äldre granskog.</t>
+          <t>Växer på sälg i flerskiktad tät äldre granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3736,22 +3740,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3769,10 +3773,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130792117</v>
+        <v>130792130</v>
       </c>
       <c r="B25" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3780,30 +3784,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540356</v>
+        <v>540421</v>
       </c>
       <c r="R25" t="n">
-        <v>6983351</v>
+        <v>6983424</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växer på sälg i flerskiktad tät äldre granskog.</t>
+          <t>På flera granar i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3876,22 +3876,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 61433-2025 artfynd.xlsx
+++ b/artfynd/A 61433-2025 artfynd.xlsx
@@ -1597,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130792125</v>
+        <v>130792115</v>
       </c>
       <c r="B9" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,26 +1608,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1635,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540336</v>
+        <v>540440</v>
       </c>
       <c r="R9" t="n">
-        <v>6983550</v>
+        <v>6983516</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1673,11 +1677,6 @@
           <t>2026-01-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1693,24 +1692,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1728,10 +1732,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130792115</v>
+        <v>130792125</v>
       </c>
       <c r="B10" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1739,30 +1743,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540440</v>
+        <v>540336</v>
       </c>
       <c r="R10" t="n">
-        <v>6983516</v>
+        <v>6983550</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1808,6 +1808,11 @@
           <t>2026-01-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1823,29 +1828,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
-        </is>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2003,37 +2003,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130792126</v>
+        <v>130792111</v>
       </c>
       <c r="B12" t="n">
-        <v>79221</v>
+        <v>80355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2041,10 +2045,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540352</v>
+        <v>540437</v>
       </c>
       <c r="R12" t="n">
-        <v>6983522</v>
+        <v>6983501</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2081,7 +2085,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Garnlav på en stående död gran med full längd och 26 cm i brösthöjdsdiameter.</t>
+          <t>På en tvåstammig sälg i bra skick.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2106,22 +2110,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2139,41 +2143,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130792111</v>
+        <v>130792126</v>
       </c>
       <c r="B13" t="n">
-        <v>80355</v>
+        <v>79221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540437</v>
+        <v>540352</v>
       </c>
       <c r="R13" t="n">
-        <v>6983501</v>
+        <v>6983522</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en tvåstammig sälg i bra skick.</t>
+          <t>Garnlav på en stående död gran med full längd och 26 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2246,22 +2246,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2674,41 +2674,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130792112</v>
+        <v>130792120</v>
       </c>
       <c r="B17" t="n">
-        <v>80355</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2716,10 +2712,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540538</v>
+        <v>540423</v>
       </c>
       <c r="R17" t="n">
-        <v>6983440</v>
+        <v>6983752</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2756,7 +2752,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På en levande skadad sälg.</t>
+          <t>På en stående död högväxt gran med full längd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2781,22 +2777,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2814,37 +2810,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130792120</v>
+        <v>130792112</v>
       </c>
       <c r="B18" t="n">
-        <v>79221</v>
+        <v>80355</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540423</v>
+        <v>540538</v>
       </c>
       <c r="R18" t="n">
-        <v>6983752</v>
+        <v>6983440</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På en stående död högväxt gran med full längd.</t>
+          <t>På en levande skadad sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2917,22 +2917,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130792117</v>
+        <v>130792130</v>
       </c>
       <c r="B24" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3644,30 +3644,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3675,10 +3671,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540356</v>
+        <v>540421</v>
       </c>
       <c r="R24" t="n">
-        <v>6983351</v>
+        <v>6983424</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3715,7 +3711,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Växer på sälg i flerskiktad tät äldre granskog.</t>
+          <t>På flera granar i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3740,22 +3736,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3773,10 +3769,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130792130</v>
+        <v>130792117</v>
       </c>
       <c r="B25" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3784,26 +3780,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540421</v>
+        <v>540356</v>
       </c>
       <c r="R25" t="n">
-        <v>6983424</v>
+        <v>6983351</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På flera granar i flerskiktad äldre granskog.</t>
+          <t>Växer på sälg i flerskiktad tät äldre granskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3876,22 +3876,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 61433-2025 artfynd.xlsx
+++ b/artfynd/A 61433-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130792129</v>
+        <v>132697172</v>
       </c>
       <c r="B2" t="n">
-        <v>79243</v>
+        <v>89354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540449</v>
+        <v>540323</v>
       </c>
       <c r="R2" t="n">
-        <v>6983399</v>
+        <v>6983539</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,17 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Gott om vidväxta fruktkroppar i en upplyft granlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,11 +775,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
-        </is>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
           <t>gran</t>
@@ -788,12 +787,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,14 +810,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130792131</v>
+        <v>130792119</v>
       </c>
       <c r="B3" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -849,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540369</v>
+        <v>540399</v>
       </c>
       <c r="R3" t="n">
-        <v>6983365</v>
+        <v>6983725</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -947,14 +946,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130792123</v>
+        <v>130792120</v>
       </c>
       <c r="B4" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -985,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540374</v>
+        <v>540423</v>
       </c>
       <c r="R4" t="n">
-        <v>6983624</v>
+        <v>6983752</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,7 +1024,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Relativt rikligt med långväxta bålar på flera granar.</t>
+          <t>På en stående död högväxt gran med full längd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,12 +1059,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1083,38 +1082,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130792114</v>
+        <v>130792121</v>
       </c>
       <c r="B5" t="n">
-        <v>97878</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1122,10 +1120,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540453</v>
+        <v>540422</v>
       </c>
       <c r="R5" t="n">
-        <v>6983484</v>
+        <v>6983701</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,6 +1158,11 @@
           <t>2026-01-19</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1178,6 +1181,26 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,14 +1218,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130792121</v>
+        <v>130792122</v>
       </c>
       <c r="B6" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1233,10 +1256,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540422</v>
+        <v>540402</v>
       </c>
       <c r="R6" t="n">
-        <v>6983701</v>
+        <v>6983656</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1273,7 +1296,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På stående död gran med full längd.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,12 +1331,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1331,14 +1354,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130792119</v>
+        <v>130792123</v>
       </c>
       <c r="B7" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1369,10 +1392,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540399</v>
+        <v>540374</v>
       </c>
       <c r="R7" t="n">
-        <v>6983725</v>
+        <v>6983624</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1432,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Relativt rikligt med långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1467,41 +1490,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130792118</v>
+        <v>130792124</v>
       </c>
       <c r="B8" t="n">
-        <v>80384</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1509,10 +1528,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540442</v>
+        <v>540353</v>
       </c>
       <c r="R8" t="n">
-        <v>6983512</v>
+        <v>6983577</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1547,6 +1566,11 @@
           <t>2026-01-19</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta uppåt ca meterlånga bålar, på gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1562,24 +1586,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1597,41 +1626,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130792116</v>
+        <v>130792125</v>
       </c>
       <c r="B9" t="n">
-        <v>80348</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1639,10 +1664,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540533</v>
+        <v>540336</v>
       </c>
       <c r="R9" t="n">
-        <v>6983434</v>
+        <v>6983550</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1679,7 +1704,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på en skadad men levande sälg.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,29 +1722,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1737,41 +1757,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130792115</v>
+        <v>130792126</v>
       </c>
       <c r="B10" t="n">
-        <v>80348</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1779,10 +1795,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540440</v>
+        <v>540352</v>
       </c>
       <c r="R10" t="n">
-        <v>6983516</v>
+        <v>6983522</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1817,6 +1833,11 @@
           <t>2026-01-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Garnlav på en stående död gran med full längd och 26 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1839,22 +1860,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1872,14 +1893,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130792125</v>
+        <v>130792127</v>
       </c>
       <c r="B11" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1910,10 +1931,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540336</v>
+        <v>540394</v>
       </c>
       <c r="R11" t="n">
-        <v>6983550</v>
+        <v>6983545</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1950,7 +1971,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2003,41 +2024,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130792111</v>
+        <v>130792128</v>
       </c>
       <c r="B12" t="n">
-        <v>80377</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2045,10 +2062,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540437</v>
+        <v>540513</v>
       </c>
       <c r="R12" t="n">
-        <v>6983501</v>
+        <v>6983413</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2083,11 +2100,6 @@
           <t>2026-01-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På en tvåstammig sälg i bra skick.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2110,22 +2122,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2143,14 +2155,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130792126</v>
+        <v>130792129</v>
       </c>
       <c r="B13" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2181,10 +2193,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540352</v>
+        <v>540449</v>
       </c>
       <c r="R13" t="n">
-        <v>6983522</v>
+        <v>6983399</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2221,7 +2233,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Garnlav på en stående död gran med full längd och 26 cm i brösthöjdsdiameter.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2256,12 +2268,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2279,61 +2291,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130792107</v>
+        <v>130792130</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Finnsjöberget Väst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540520</v>
+        <v>540421</v>
       </c>
       <c r="R14" t="n">
-        <v>6983418</v>
+        <v>6983424</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2370,7 +2369,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Synobservation av 1 födosökande individ. Hann ej se om det var hona eller hane. Minst medelhögt till högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
+          <t>På flera granar i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2379,6 +2378,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2389,7 +2389,27 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn. Gott om stående död ved främst av gran i denna skog där många partier indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2407,14 +2427,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130792132</v>
+        <v>130792131</v>
       </c>
       <c r="B15" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2445,10 +2465,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540329</v>
+        <v>540369</v>
       </c>
       <c r="R15" t="n">
-        <v>6983376</v>
+        <v>6983365</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2485,7 +2505,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På flera granar i tät äldre flerskiktad granskog.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2543,14 +2563,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130792127</v>
+        <v>130792132</v>
       </c>
       <c r="B16" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2581,10 +2601,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540394</v>
+        <v>540329</v>
       </c>
       <c r="R16" t="n">
-        <v>6983545</v>
+        <v>6983376</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2621,7 +2641,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På flera granar i tät äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2637,6 +2657,11 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2674,14 +2699,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130792120</v>
+        <v>132697170</v>
       </c>
       <c r="B17" t="n">
-        <v>79243</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2712,10 +2737,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540423</v>
+        <v>540277</v>
       </c>
       <c r="R17" t="n">
-        <v>6983752</v>
+        <v>6983497</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2742,17 +2767,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På en stående död högväxt gran med full längd.</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2770,11 +2790,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2787,12 +2802,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2810,41 +2825,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130792112</v>
+        <v>132697171</v>
       </c>
       <c r="B18" t="n">
-        <v>80377</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2852,10 +2863,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540538</v>
+        <v>540317</v>
       </c>
       <c r="R18" t="n">
-        <v>6983440</v>
+        <v>6983509</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2882,17 +2893,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På en levande skadad sälg.</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2910,29 +2916,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2950,39 +2951,39 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130792110</v>
+        <v>130792115</v>
       </c>
       <c r="B19" t="n">
-        <v>80377</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2992,10 +2993,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540404</v>
+        <v>540440</v>
       </c>
       <c r="R19" t="n">
-        <v>6983759</v>
+        <v>6983516</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3028,11 +3029,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På en halvt fallen grov levande sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3090,10 +3086,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130792128</v>
+        <v>130792116</v>
       </c>
       <c r="B20" t="n">
-        <v>79243</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3101,26 +3097,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540513</v>
+        <v>540533</v>
       </c>
       <c r="R20" t="n">
-        <v>6983413</v>
+        <v>6983434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3166,6 +3166,11 @@
           <t>2026-01-19</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apothecier på en skadad men levande sälg.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3188,22 +3193,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3221,10 +3226,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130792124</v>
+        <v>130792117</v>
       </c>
       <c r="B21" t="n">
-        <v>79243</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3232,26 +3237,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3259,10 +3268,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540353</v>
+        <v>540356</v>
       </c>
       <c r="R21" t="n">
-        <v>6983577</v>
+        <v>6983351</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3299,7 +3308,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta uppåt ca meterlånga bålar, på gran.</t>
+          <t>Växer på sälg i flerskiktad tät äldre granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3324,22 +3333,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3357,10 +3366,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130792122</v>
+        <v>132697166</v>
       </c>
       <c r="B22" t="n">
-        <v>79243</v>
+        <v>80488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3368,26 +3377,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3395,10 +3408,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540402</v>
+        <v>540295</v>
       </c>
       <c r="R22" t="n">
-        <v>6983656</v>
+        <v>6983484</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3425,17 +3438,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På flera gamla granar.</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3453,29 +3461,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
-        </is>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3493,40 +3496,39 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130792113</v>
+        <v>130792110</v>
       </c>
       <c r="B23" t="n">
-        <v>57881</v>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3536,10 +3538,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540363</v>
+        <v>540404</v>
       </c>
       <c r="R23" t="n">
-        <v>6983365</v>
+        <v>6983759</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3576,7 +3578,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rejäla äldre hackspår i en liggande granlåga.</t>
+          <t>På en halvt fallen grov levande sälg.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3585,6 +3587,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3600,22 +3603,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3633,37 +3636,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130792130</v>
+        <v>130792111</v>
       </c>
       <c r="B24" t="n">
-        <v>79243</v>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3671,10 +3678,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540421</v>
+        <v>540437</v>
       </c>
       <c r="R24" t="n">
-        <v>6983424</v>
+        <v>6983501</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3711,7 +3718,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På flera granar i flerskiktad äldre granskog.</t>
+          <t>På en tvåstammig sälg i bra skick.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3736,22 +3743,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3769,39 +3776,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130792117</v>
+        <v>130792112</v>
       </c>
       <c r="B25" t="n">
-        <v>80348</v>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3811,10 +3818,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540356</v>
+        <v>540538</v>
       </c>
       <c r="R25" t="n">
-        <v>6983351</v>
+        <v>6983440</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3851,7 +3858,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växer på sälg i flerskiktad tät äldre granskog.</t>
+          <t>På en levande skadad sälg.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3909,65 +3916,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130792108</v>
+        <v>132697163</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>80493</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Finnsjöberget Väst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540370</v>
+        <v>540280</v>
       </c>
       <c r="R26" t="n">
-        <v>6983374</v>
+        <v>6983505</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3994,17 +3988,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>En hane som födosökte på en stående död gran med full längd och 31 cm i brösthöjdsdiameter. Mycket högt livsmiljövärde för tretåig hackspett baserat på stående död ved av gran på/kring fyndplatsen. Gott om stående döda granar här.</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4013,6 +4002,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4021,9 +4011,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn. Gott om stående död ved främst av gran i denna skog där många partier indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4041,40 +4046,39 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130792106</v>
+        <v>130792118</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>80468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4084,10 +4088,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540343</v>
+        <v>540442</v>
       </c>
       <c r="R27" t="n">
-        <v>6983569</v>
+        <v>6983512</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4122,17 +4126,13 @@
           <t>2026-01-19</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, i riklig mängd på en gammal grov gran.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4141,29 +4141,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn. Gott om stående död ved främst av gran i denna skog där många partier indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4181,65 +4176,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132697168</v>
+        <v>130792113</v>
       </c>
       <c r="B28" t="n">
-        <v>99130</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Finnsjöberget Väst, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540326</v>
+        <v>540363</v>
       </c>
       <c r="R28" t="n">
-        <v>6983468</v>
+        <v>6983365</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4266,17 +4249,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 3 vinterståndare inom ca 1 m2 yta.</t>
+          <t>Rejäla äldre hackspår i en liggande granlåga.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4285,13 +4268,37 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4309,10 +4316,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132697166</v>
+        <v>130792106</v>
       </c>
       <c r="B29" t="n">
-        <v>80438</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4320,28 +4327,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4351,10 +4359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540295</v>
+        <v>540343</v>
       </c>
       <c r="R29" t="n">
-        <v>6983484</v>
+        <v>6983569</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4381,12 +4389,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, i riklig mängd på en gammal grov gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4395,7 +4408,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4404,24 +4416,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn. Gott om stående död ved främst av gran i denna skog där många partier indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4439,10 +4456,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132697170</v>
+        <v>130792107</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4450,37 +4467,50 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Finnsjöberget Väst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540277</v>
+        <v>540520</v>
       </c>
       <c r="R30" t="n">
-        <v>6983497</v>
+        <v>6983418</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4507,12 +4537,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 födosökande individ. Hann ej se om det var hona eller hane. Minst medelhögt till högt livsmiljövärde för tretåig hackspett på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4521,7 +4556,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4530,24 +4564,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn. Gott om stående död ved främst av gran i denna skog där många partier indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4565,50 +4584,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132697169</v>
+        <v>130792108</v>
       </c>
       <c r="B31" t="n">
-        <v>99130</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4620,10 +4639,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540327</v>
+        <v>540370</v>
       </c>
       <c r="R31" t="n">
-        <v>6983537</v>
+        <v>6983374</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4650,17 +4669,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog. Flera nya blomstjälkar på gång.</t>
+          <t>En hane som födosökte på en stående död gran med full längd och 31 cm i brösthöjdsdiameter. Mycket högt livsmiljövärde för tretåig hackspett baserat på stående död ved av gran på/kring fyndplatsen. Gott om stående döda granar här.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4669,13 +4688,17 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn. Gott om stående död ved främst av gran i denna skog där många partier indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4693,41 +4716,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132697172</v>
+        <v>132697167</v>
       </c>
       <c r="B32" t="n">
-        <v>89300</v>
+        <v>111153</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>220240</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4735,10 +4759,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540323</v>
+        <v>540356</v>
       </c>
       <c r="R32" t="n">
-        <v>6983539</v>
+        <v>6983533</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4773,11 +4797,6 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Gott om vidväxta fruktkroppar i en upplyft granlåga.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4791,26 +4810,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4828,48 +4827,65 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132697171</v>
+        <v>132697168</v>
       </c>
       <c r="B33" t="n">
-        <v>79333</v>
+        <v>99195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Finnsjöberget Väst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540317</v>
+        <v>540326</v>
       </c>
       <c r="R33" t="n">
-        <v>6983509</v>
+        <v>6983468</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4904,6 +4920,11 @@
           <t>2026-04-21</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 100 plantor och 3 vinterståndare inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4917,26 +4938,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4954,49 +4955,65 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132697165</v>
+        <v>132697169</v>
       </c>
       <c r="B34" t="n">
-        <v>98001</v>
+        <v>99195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Finnsjöberget Väst, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540348</v>
+        <v>540327</v>
       </c>
       <c r="R34" t="n">
-        <v>6983457</v>
+        <v>6983537</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5033,7 +5050,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gott om plattlummer här.</t>
+          <t>Minst 110 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog. Flera nya blomstjälkar på gång.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5066,10 +5083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132697163</v>
+        <v>132697162</v>
       </c>
       <c r="B35" t="n">
-        <v>80467</v>
+        <v>106309</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5077,30 +5094,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5108,10 +5126,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540280</v>
+        <v>540300</v>
       </c>
       <c r="R35" t="n">
-        <v>6983505</v>
+        <v>6983493</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5146,6 +5164,11 @@
           <t>2026-04-21</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Frökapsel och gröna blad.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5159,26 +5182,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5196,10 +5199,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132697164</v>
+        <v>132697165</v>
       </c>
       <c r="B36" t="n">
-        <v>97995</v>
+        <v>98066</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5207,16 +5210,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5235,10 +5238,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540294</v>
+        <v>540348</v>
       </c>
       <c r="R36" t="n">
-        <v>6983444</v>
+        <v>6983457</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5271,6 +5274,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gott om plattlummer här.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5303,10 +5311,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132697162</v>
+        <v>130792114</v>
       </c>
       <c r="B37" t="n">
-        <v>106243</v>
+        <v>97983</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5314,30 +5322,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
@@ -5346,10 +5350,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540300</v>
+        <v>540453</v>
       </c>
       <c r="R37" t="n">
-        <v>6983493</v>
+        <v>6983484</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5376,17 +5380,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Frökapsel och gröna blad.</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5404,6 +5403,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad granskog med inslag av björk, sälg, tall asp och rönn.</t>
+        </is>
+      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
@@ -5416,6 +5420,113 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132697164</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Finnsjöberget Väst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>540294</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6983444</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61433-2025 artfynd.xlsx
+++ b/artfynd/A 61433-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132697172</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -943,6 +953,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792119</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1079,6 +1094,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792120</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1215,6 +1235,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792121</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1351,6 +1376,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792122</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1487,6 +1517,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792123</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1623,6 +1658,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792124</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1754,6 +1794,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792125</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1890,6 +1935,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792126</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2021,6 +2071,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792127</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2152,6 +2207,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792128</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2288,6 +2348,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792129</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2424,6 +2489,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792130</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2560,6 +2630,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792131</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2696,6 +2771,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792132</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2822,6 +2902,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132697170</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2948,6 +3033,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132697171</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3083,6 +3173,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792115</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3223,6 +3318,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792116</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3363,6 +3463,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792117</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3493,6 +3598,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132697166</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3633,6 +3743,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792110</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3773,6 +3888,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792111</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3913,6 +4033,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792112</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4043,6 +4168,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132697163</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4173,6 +4303,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792118</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4313,6 +4448,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792113</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4453,6 +4593,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792106</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4581,6 +4726,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792107</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4713,6 +4863,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792108</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4824,6 +4979,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132697167</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4952,6 +5112,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132697168</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5080,6 +5245,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132697169</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5196,6 +5366,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132697162</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5308,6 +5483,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132697165</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5420,6 +5600,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792114</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5527,8 +5712,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132697164</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>